--- a/gstdatabase/GSTR-3B-2020-2021.xlsx
+++ b/gstdatabase/GSTR-3B-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A13C1-9E22-4FB9-BDEB-BD9713799451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF577A77-F313-489A-9A3B-303317806455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="E12" s="17">
         <f t="shared" si="0"/>
-        <v>270113</v>
+        <v>270114</v>
       </c>
       <c r="F12" s="16">
-        <v>291588</v>
+        <v>291589</v>
       </c>
       <c r="G12" s="18">
         <f t="shared" si="1"/>
-        <v>0.93444214776714896</v>
+        <v>0.93444535243314264</v>
       </c>
       <c r="H12" s="7">
         <v>311421</v>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="J12" s="17">
         <f t="shared" si="2"/>
-        <v>211656</v>
+        <v>211657</v>
       </c>
       <c r="K12" s="16">
-        <v>291495</v>
+        <v>291496</v>
       </c>
       <c r="L12" s="18">
         <f t="shared" si="3"/>
-        <v>0.93601587561532462</v>
+        <v>0.93601908670256662</v>
       </c>
       <c r="M12" s="7">
         <v>312776</v>
@@ -1612,14 +1612,14 @@
       </c>
       <c r="O12" s="17">
         <f t="shared" si="4"/>
-        <v>165095</v>
+        <v>165096</v>
       </c>
       <c r="P12" s="16">
-        <v>292498</v>
+        <v>292499</v>
       </c>
       <c r="Q12" s="18">
         <f t="shared" si="5"/>
-        <v>0.93516765992275619</v>
+        <v>0.93517085709901016</v>
       </c>
       <c r="R12" s="7">
         <v>313307</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="T12" s="17">
         <f t="shared" si="6"/>
-        <v>160589</v>
+        <v>160590</v>
       </c>
       <c r="U12" s="16">
-        <v>295227</v>
+        <v>295228</v>
       </c>
       <c r="V12" s="18">
         <f t="shared" si="7"/>
-        <v>0.9422930224986994</v>
+        <v>0.9422962142563045</v>
       </c>
       <c r="W12" s="7">
         <v>316396</v>
@@ -1646,14 +1646,14 @@
       </c>
       <c r="Y12" s="17">
         <f t="shared" si="8"/>
-        <v>116006</v>
+        <v>116007</v>
       </c>
       <c r="Z12" s="16">
-        <v>297518</v>
+        <v>297519</v>
       </c>
       <c r="AA12" s="18">
         <f t="shared" si="9"/>
-        <v>0.94033426465568459</v>
+        <v>0.94033742525189956</v>
       </c>
       <c r="AB12" s="28">
         <v>318929</v>
@@ -1663,14 +1663,14 @@
       </c>
       <c r="AD12" s="17">
         <f t="shared" si="10"/>
-        <v>60001</v>
+        <v>60002</v>
       </c>
       <c r="AE12" s="40">
-        <v>299266</v>
+        <v>299267</v>
       </c>
       <c r="AF12" s="18">
         <f t="shared" si="11"/>
-        <v>0.93834677937722821</v>
+        <v>0.93834991487133501</v>
       </c>
       <c r="AG12" s="16">
         <v>321958</v>
@@ -1680,14 +1680,14 @@
       </c>
       <c r="AI12" s="17">
         <f t="shared" si="12"/>
-        <v>53871</v>
+        <v>53872</v>
       </c>
       <c r="AJ12" s="16">
-        <v>301289</v>
+        <v>301290</v>
       </c>
       <c r="AK12" s="18">
         <f t="shared" si="13"/>
-        <v>0.93580218537821702</v>
+        <v>0.93580529137340895</v>
       </c>
       <c r="AL12" s="30">
         <v>323060</v>
@@ -1697,14 +1697,14 @@
       </c>
       <c r="AN12" s="17">
         <f t="shared" si="14"/>
-        <v>48756</v>
+        <v>48757</v>
       </c>
       <c r="AO12" s="16">
-        <v>302906</v>
+        <v>302907</v>
       </c>
       <c r="AP12" s="18">
         <f t="shared" si="15"/>
-        <v>0.93761530365876311</v>
+        <v>0.93761839905899835</v>
       </c>
       <c r="AQ12" s="32">
         <v>323550</v>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="AS12" s="17">
         <f t="shared" si="16"/>
-        <v>41154</v>
+        <v>41155</v>
       </c>
       <c r="AT12" s="16">
-        <v>304434</v>
+        <v>304435</v>
       </c>
       <c r="AU12" s="18">
         <f t="shared" si="17"/>
-        <v>0.94091794158553543</v>
+        <v>0.94092103229794466</v>
       </c>
       <c r="AV12" s="34">
         <v>144815</v>
@@ -1731,14 +1731,14 @@
       </c>
       <c r="AX12" s="17">
         <f t="shared" si="18"/>
-        <v>34989</v>
+        <v>34990</v>
       </c>
       <c r="AY12" s="19">
-        <v>130386</v>
+        <v>130387</v>
       </c>
       <c r="AZ12" s="18">
         <f t="shared" si="19"/>
-        <v>0.90036253150571421</v>
+        <v>0.90036943686772775</v>
       </c>
       <c r="BA12" s="36">
         <v>144139</v>
@@ -1748,14 +1748,14 @@
       </c>
       <c r="BC12" s="17">
         <f t="shared" si="20"/>
-        <v>29050</v>
+        <v>29051</v>
       </c>
       <c r="BD12" s="38">
-        <v>133016</v>
+        <v>133017</v>
       </c>
       <c r="BE12" s="18">
         <f t="shared" si="21"/>
-        <v>0.92283143354678465</v>
+        <v>0.92283837129437551</v>
       </c>
       <c r="BF12" s="9">
         <v>318519</v>
@@ -1765,14 +1765,14 @@
       </c>
       <c r="BH12" s="17">
         <f t="shared" si="22"/>
-        <v>63436</v>
+        <v>63437</v>
       </c>
       <c r="BI12" s="19">
-        <v>308495</v>
+        <v>308496</v>
       </c>
       <c r="BJ12" s="18">
         <f t="shared" si="23"/>
-        <v>0.9685293498974944</v>
+        <v>0.96853248942763226</v>
       </c>
       <c r="BK12" s="2"/>
       <c r="BL12" s="2"/>
@@ -2536,14 +2536,14 @@
       </c>
       <c r="AI16" s="17">
         <f t="shared" si="12"/>
-        <v>177859</v>
+        <v>177860</v>
       </c>
       <c r="AJ16" s="16">
-        <v>672059</v>
+        <v>672060</v>
       </c>
       <c r="AK16" s="18">
         <f t="shared" si="13"/>
-        <v>0.86398007877983807</v>
+        <v>0.86398136435160899</v>
       </c>
       <c r="AL16" s="30">
         <v>781370</v>
@@ -2553,14 +2553,14 @@
       </c>
       <c r="AN16" s="17">
         <f t="shared" si="14"/>
-        <v>145970</v>
+        <v>145972</v>
       </c>
       <c r="AO16" s="16">
-        <v>677856</v>
+        <v>677858</v>
       </c>
       <c r="AP16" s="18">
         <f t="shared" si="15"/>
-        <v>0.86752242855497397</v>
+        <v>0.86752498816181833</v>
       </c>
       <c r="AQ16" s="32">
         <v>767321</v>
@@ -2570,14 +2570,14 @@
       </c>
       <c r="AS16" s="17">
         <f t="shared" si="16"/>
-        <v>117273</v>
+        <v>117275</v>
       </c>
       <c r="AT16" s="16">
-        <v>681917</v>
+        <v>681919</v>
       </c>
       <c r="AU16" s="18">
         <f t="shared" si="17"/>
-        <v>0.88869847169567884</v>
+        <v>0.88870107816676458</v>
       </c>
       <c r="AV16" s="34">
         <v>376545</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="J17" s="17">
         <f t="shared" si="2"/>
-        <v>371935</v>
+        <v>371936</v>
       </c>
       <c r="K17" s="16">
-        <v>518977</v>
+        <v>518978</v>
       </c>
       <c r="L17" s="18">
         <f t="shared" si="3"/>
-        <v>0.94338357058330591</v>
+        <v>0.94338538835860342</v>
       </c>
       <c r="M17" s="7">
         <v>556868</v>
@@ -2682,14 +2682,14 @@
       </c>
       <c r="O17" s="17">
         <f t="shared" si="4"/>
-        <v>312466</v>
+        <v>312468</v>
       </c>
       <c r="P17" s="16">
-        <v>525548</v>
+        <v>525550</v>
       </c>
       <c r="Q17" s="18">
         <f t="shared" si="5"/>
-        <v>0.94375686877321019</v>
+        <v>0.94376046028861416</v>
       </c>
       <c r="R17" s="7">
         <v>565483</v>
@@ -2818,14 +2818,14 @@
       </c>
       <c r="BC17" s="17">
         <f t="shared" si="20"/>
-        <v>66017</v>
+        <v>66019</v>
       </c>
       <c r="BD17" s="38">
-        <v>242530</v>
+        <v>242532</v>
       </c>
       <c r="BE17" s="18">
         <f t="shared" si="21"/>
-        <v>0.95556860133881261</v>
+        <v>0.95557648134212214</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2835,14 +2835,14 @@
       </c>
       <c r="BH17" s="17">
         <f t="shared" si="22"/>
-        <v>190044</v>
+        <v>190045</v>
       </c>
       <c r="BI17" s="19">
-        <v>582502</v>
+        <v>582503</v>
       </c>
       <c r="BJ17" s="18">
         <f t="shared" si="23"/>
-        <v>0.98599469172749066</v>
+        <v>0.98599638441642856</v>
       </c>
       <c r="BK17" s="2"/>
       <c r="BL17" s="2"/>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AN18" s="17">
         <f t="shared" si="14"/>
-        <v>215686</v>
+        <v>215687</v>
       </c>
       <c r="AO18" s="16">
-        <v>1138633</v>
+        <v>1138634</v>
       </c>
       <c r="AP18" s="18">
         <f t="shared" si="15"/>
-        <v>0.92137841855391645</v>
+        <v>0.92137922775092596</v>
       </c>
       <c r="AQ18" s="32">
         <v>1231355</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AS18" s="17">
         <f t="shared" si="16"/>
-        <v>183800</v>
+        <v>183801</v>
       </c>
       <c r="AT18" s="16">
-        <v>1149654</v>
+        <v>1149655</v>
       </c>
       <c r="AU18" s="18">
         <f t="shared" si="17"/>
-        <v>0.93364951618339143</v>
+        <v>0.93365032829687622</v>
       </c>
       <c r="AV18" s="34">
         <v>676084</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="AX18" s="17">
         <f t="shared" si="18"/>
-        <v>184449</v>
+        <v>184450</v>
       </c>
       <c r="AY18" s="19">
-        <v>606981</v>
+        <v>606982</v>
       </c>
       <c r="AZ18" s="18">
         <f t="shared" si="19"/>
-        <v>0.89778932795333122</v>
+        <v>0.89779080705947778</v>
       </c>
       <c r="BA18" s="36">
         <v>651597</v>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="BC18" s="17">
         <f t="shared" si="20"/>
-        <v>154177</v>
+        <v>154178</v>
       </c>
       <c r="BD18" s="38">
-        <v>620518</v>
+        <v>620519</v>
       </c>
       <c r="BE18" s="18">
         <f t="shared" si="21"/>
-        <v>0.95230334086866575</v>
+        <v>0.95230487555958665</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="BH18" s="17">
         <f t="shared" si="22"/>
-        <v>356601</v>
+        <v>356602</v>
       </c>
       <c r="BI18" s="19">
-        <v>1175749</v>
+        <v>1175750</v>
       </c>
       <c r="BJ18" s="18">
         <f t="shared" si="23"/>
-        <v>0.9772840996178136</v>
+        <v>0.9772849308191156</v>
       </c>
       <c r="BK18" s="2"/>
       <c r="BL18" s="2"/>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="Y19" s="17">
         <f t="shared" si="8"/>
-        <v>151053</v>
+        <v>151054</v>
       </c>
       <c r="Z19" s="16">
-        <v>309571</v>
+        <v>309572</v>
       </c>
       <c r="AA19" s="18">
         <f t="shared" si="9"/>
-        <v>0.90128334274684263</v>
+        <v>0.9012862541414588</v>
       </c>
       <c r="AB19" s="28">
         <v>355383</v>
@@ -3161,14 +3161,14 @@
       </c>
       <c r="AD19" s="17">
         <f t="shared" si="10"/>
-        <v>93728</v>
+        <v>93729</v>
       </c>
       <c r="AE19" s="40">
-        <v>315649</v>
+        <v>315650</v>
       </c>
       <c r="AF19" s="18">
         <f t="shared" si="11"/>
-        <v>0.88819386408466361</v>
+        <v>0.88819667795026769</v>
       </c>
       <c r="AG19" s="16">
         <v>365633</v>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="AI19" s="17">
         <f t="shared" si="12"/>
-        <v>109290</v>
+        <v>109291</v>
       </c>
       <c r="AJ19" s="16">
-        <v>321347</v>
+        <v>321348</v>
       </c>
       <c r="AK19" s="18">
         <f t="shared" si="13"/>
-        <v>0.87887854761468465</v>
+        <v>0.87888128259757736</v>
       </c>
       <c r="AL19" s="30">
         <v>370137</v>
@@ -3195,14 +3195,14 @@
       </c>
       <c r="AN19" s="17">
         <f t="shared" si="14"/>
-        <v>84853</v>
+        <v>84854</v>
       </c>
       <c r="AO19" s="16">
-        <v>324814</v>
+        <v>324815</v>
       </c>
       <c r="AP19" s="18">
         <f t="shared" si="15"/>
-        <v>0.87755074472425076</v>
+        <v>0.87755344642659339</v>
       </c>
       <c r="AQ19" s="32">
         <v>372999</v>
@@ -3212,14 +3212,14 @@
       </c>
       <c r="AS19" s="17">
         <f t="shared" si="16"/>
-        <v>67758</v>
+        <v>67759</v>
       </c>
       <c r="AT19" s="16">
-        <v>329625</v>
+        <v>329626</v>
       </c>
       <c r="AU19" s="18">
         <f t="shared" si="17"/>
-        <v>0.88371550593969417</v>
+        <v>0.8837181869120293</v>
       </c>
       <c r="AV19" s="34">
         <v>223052</v>
@@ -3229,14 +3229,14 @@
       </c>
       <c r="AX19" s="17">
         <f t="shared" si="18"/>
-        <v>71737</v>
+        <v>71738</v>
       </c>
       <c r="AY19" s="19">
-        <v>180729</v>
+        <v>180730</v>
       </c>
       <c r="AZ19" s="18">
         <f t="shared" si="19"/>
-        <v>0.81025500780087156</v>
+        <v>0.81025949106038053</v>
       </c>
       <c r="BA19" s="36">
         <v>218640</v>
@@ -3246,14 +3246,14 @@
       </c>
       <c r="BC19" s="17">
         <f t="shared" si="20"/>
-        <v>58336</v>
+        <v>58337</v>
       </c>
       <c r="BD19" s="38">
-        <v>187543</v>
+        <v>187544</v>
       </c>
       <c r="BE19" s="18">
         <f t="shared" si="21"/>
-        <v>0.85777076472740577</v>
+        <v>0.85777533845590925</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3263,14 +3263,14 @@
       </c>
       <c r="BH19" s="17">
         <f t="shared" si="22"/>
-        <v>121137</v>
+        <v>121138</v>
       </c>
       <c r="BI19" s="19">
-        <v>346120</v>
+        <v>346121</v>
       </c>
       <c r="BJ19" s="18">
         <f t="shared" si="23"/>
-        <v>0.91868477210714627</v>
+        <v>0.9186874263449023</v>
       </c>
       <c r="BK19" s="2"/>
       <c r="BL19" s="2"/>
@@ -4102,14 +4102,14 @@
       </c>
       <c r="BC23" s="17">
         <f t="shared" si="20"/>
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="BD23" s="38">
-        <v>6828</v>
+        <v>6829</v>
       </c>
       <c r="BE23" s="18">
         <f t="shared" si="21"/>
-        <v>0.73340494092373787</v>
+        <v>0.73351235230934475</v>
       </c>
       <c r="BF23" s="9">
         <v>10990</v>
@@ -4119,14 +4119,14 @@
       </c>
       <c r="BH23" s="17">
         <f t="shared" si="22"/>
-        <v>4115</v>
+        <v>4116</v>
       </c>
       <c r="BI23" s="19">
-        <v>8771</v>
+        <v>8772</v>
       </c>
       <c r="BJ23" s="18">
         <f t="shared" si="23"/>
-        <v>0.79808917197452234</v>
+        <v>0.79818016378525936</v>
       </c>
       <c r="BK23" s="2"/>
       <c r="BL23" s="2"/>
@@ -4146,14 +4146,14 @@
       </c>
       <c r="E24" s="17">
         <f t="shared" si="0"/>
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="F24" s="16">
-        <v>4791</v>
+        <v>4792</v>
       </c>
       <c r="G24" s="18">
         <f t="shared" si="1"/>
-        <v>0.77025723472668806</v>
+        <v>0.77041800643086822</v>
       </c>
       <c r="H24" s="7">
         <v>6236</v>
@@ -4163,14 +4163,14 @@
       </c>
       <c r="J24" s="17">
         <f t="shared" si="2"/>
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="K24" s="16">
-        <v>4808</v>
+        <v>4809</v>
       </c>
       <c r="L24" s="18">
         <f t="shared" si="3"/>
-        <v>0.77100705580500317</v>
+        <v>0.7711674150096216</v>
       </c>
       <c r="M24" s="7">
         <v>6293</v>
@@ -4180,14 +4180,14 @@
       </c>
       <c r="O24" s="17">
         <f t="shared" si="4"/>
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="P24" s="16">
-        <v>4836</v>
+        <v>4837</v>
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="5"/>
-        <v>0.76847290640394084</v>
+        <v>0.76863181312569517</v>
       </c>
       <c r="R24" s="7">
         <v>6429</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="T24" s="17">
         <f t="shared" si="6"/>
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="U24" s="16">
-        <v>4912</v>
+        <v>4913</v>
       </c>
       <c r="V24" s="18">
         <f t="shared" si="7"/>
-        <v>0.76403795302535382</v>
+        <v>0.76419349821123039</v>
       </c>
       <c r="W24" s="7">
         <v>6586</v>
@@ -4214,14 +4214,14 @@
       </c>
       <c r="Y24" s="17">
         <f t="shared" si="8"/>
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="Z24" s="16">
-        <v>4977</v>
+        <v>4978</v>
       </c>
       <c r="AA24" s="18">
         <f t="shared" si="9"/>
-        <v>0.75569389614333438</v>
+        <v>0.75584573337382321</v>
       </c>
       <c r="AB24" s="28">
         <v>6663</v>
@@ -4231,14 +4231,14 @@
       </c>
       <c r="AD24" s="17">
         <f t="shared" si="10"/>
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="AE24" s="40">
-        <v>4976</v>
+        <v>4977</v>
       </c>
       <c r="AF24" s="18">
         <f t="shared" si="11"/>
-        <v>0.74681074591025065</v>
+        <v>0.74696082845565059</v>
       </c>
       <c r="AG24" s="16">
         <v>6801</v>
@@ -4248,14 +4248,14 @@
       </c>
       <c r="AI24" s="17">
         <f t="shared" si="12"/>
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AJ24" s="16">
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="AK24" s="18">
         <f t="shared" si="13"/>
-        <v>0.74165563887663577</v>
+        <v>0.74180267607704753</v>
       </c>
       <c r="AL24" s="30">
         <v>6877</v>
@@ -4265,14 +4265,14 @@
       </c>
       <c r="AN24" s="17">
         <f t="shared" si="14"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="AO24" s="16">
-        <v>5148</v>
+        <v>5149</v>
       </c>
       <c r="AP24" s="18">
         <f t="shared" si="15"/>
-        <v>0.74858223062381857</v>
+        <v>0.74872764286752946</v>
       </c>
       <c r="AQ24" s="32">
         <v>6826</v>
@@ -4282,14 +4282,14 @@
       </c>
       <c r="AS24" s="17">
         <f t="shared" si="16"/>
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="AT24" s="16">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="AU24" s="18">
         <f t="shared" si="17"/>
-        <v>0.77219455024904771</v>
+        <v>0.77234104893055966</v>
       </c>
       <c r="AV24" s="34">
         <v>5390</v>
@@ -4530,14 +4530,14 @@
       </c>
       <c r="BC25" s="17">
         <f t="shared" si="20"/>
-        <v>3689</v>
+        <v>3690</v>
       </c>
       <c r="BD25" s="38">
-        <v>13005</v>
+        <v>13006</v>
       </c>
       <c r="BE25" s="18">
         <f t="shared" si="21"/>
-        <v>0.83930300096805421</v>
+        <v>0.8393675379154566</v>
       </c>
       <c r="BF25" s="9">
         <v>25465</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="BH25" s="17">
         <f t="shared" si="22"/>
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="BI25" s="19">
-        <v>23145</v>
+        <v>23146</v>
       </c>
       <c r="BJ25" s="18">
         <f t="shared" si="23"/>
-        <v>0.90889456116237977</v>
+        <v>0.90893383074808565</v>
       </c>
       <c r="BK25" s="2"/>
       <c r="BL25" s="2"/>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="T26" s="17">
         <f t="shared" si="6"/>
-        <v>11886</v>
+        <v>11887</v>
       </c>
       <c r="U26" s="16">
-        <v>20952</v>
+        <v>20953</v>
       </c>
       <c r="V26" s="18">
         <f t="shared" si="7"/>
-        <v>0.8153798256537983</v>
+        <v>0.81541874221668742</v>
       </c>
       <c r="W26" s="7">
         <v>25913</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="AD26" s="17">
         <f t="shared" si="10"/>
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="AE26" s="40">
-        <v>21122</v>
+        <v>21123</v>
       </c>
       <c r="AF26" s="18">
         <f t="shared" si="11"/>
-        <v>0.8231809501539421</v>
+        <v>0.82321992283409329</v>
       </c>
       <c r="AG26" s="16">
         <v>26031</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="AI26" s="17">
         <f t="shared" si="12"/>
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="AJ26" s="16">
-        <v>21365</v>
+        <v>21366</v>
       </c>
       <c r="AK26" s="18">
         <f t="shared" si="13"/>
-        <v>0.82075218009296613</v>
+        <v>0.82079059582805114</v>
       </c>
       <c r="AL26" s="30">
         <v>26186</v>
@@ -4693,14 +4693,14 @@
       </c>
       <c r="AN26" s="17">
         <f t="shared" si="14"/>
-        <v>5714</v>
+        <v>5715</v>
       </c>
       <c r="AO26" s="16">
-        <v>21526</v>
+        <v>21527</v>
       </c>
       <c r="AP26" s="18">
         <f t="shared" si="15"/>
-        <v>0.82204231268616823</v>
+        <v>0.82208050103108532</v>
       </c>
       <c r="AQ26" s="32">
         <v>26317</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="AS26" s="17">
         <f t="shared" si="16"/>
-        <v>5045</v>
+        <v>5046</v>
       </c>
       <c r="AT26" s="16">
-        <v>21712</v>
+        <v>21713</v>
       </c>
       <c r="AU26" s="18">
         <f t="shared" si="17"/>
-        <v>0.8250180491697382</v>
+        <v>0.82505604742181859</v>
       </c>
       <c r="AV26" s="34">
         <v>16878</v>
@@ -4727,14 +4727,14 @@
       </c>
       <c r="AX26" s="17">
         <f t="shared" si="18"/>
-        <v>4826</v>
+        <v>4827</v>
       </c>
       <c r="AY26" s="19">
-        <v>12422</v>
+        <v>12423</v>
       </c>
       <c r="AZ26" s="18">
         <f t="shared" si="19"/>
-        <v>0.73598767626496031</v>
+        <v>0.73604692499111268</v>
       </c>
       <c r="BA26" s="36">
         <v>16504</v>
@@ -4744,14 +4744,14 @@
       </c>
       <c r="BC26" s="17">
         <f t="shared" si="20"/>
-        <v>4228</v>
+        <v>4229</v>
       </c>
       <c r="BD26" s="38">
-        <v>12482</v>
+        <v>12483</v>
       </c>
       <c r="BE26" s="18">
         <f t="shared" si="21"/>
-        <v>0.75630150266602036</v>
+        <v>0.75636209403780896</v>
       </c>
       <c r="BF26" s="9">
         <v>25358</v>
@@ -4761,14 +4761,14 @@
       </c>
       <c r="BH26" s="17">
         <f t="shared" si="22"/>
-        <v>6170</v>
+        <v>6172</v>
       </c>
       <c r="BI26" s="19">
-        <v>21812</v>
+        <v>21814</v>
       </c>
       <c r="BJ26" s="18">
         <f t="shared" si="23"/>
-        <v>0.86016247338118146</v>
+        <v>0.86024134395457053</v>
       </c>
       <c r="BK26" s="2"/>
       <c r="BL26" s="2"/>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="E27" s="17">
         <f t="shared" si="0"/>
-        <v>115195</v>
+        <v>115196</v>
       </c>
       <c r="F27" s="16">
-        <v>129453</v>
+        <v>129454</v>
       </c>
       <c r="G27" s="18">
         <f t="shared" si="1"/>
-        <v>0.88860592664795002</v>
+        <v>0.88861279096107249</v>
       </c>
       <c r="H27" s="7">
         <v>145010</v>
@@ -4805,14 +4805,14 @@
       </c>
       <c r="J27" s="17">
         <f t="shared" si="2"/>
-        <v>98116</v>
+        <v>98117</v>
       </c>
       <c r="K27" s="16">
-        <v>129428</v>
+        <v>129429</v>
       </c>
       <c r="L27" s="18">
         <f t="shared" si="3"/>
-        <v>0.89254534170057243</v>
+        <v>0.892552237776705</v>
       </c>
       <c r="M27" s="7">
         <v>146684</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="O27" s="17">
         <f t="shared" si="4"/>
-        <v>98020</v>
+        <v>98021</v>
       </c>
       <c r="P27" s="16">
-        <v>130616</v>
+        <v>130617</v>
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="5"/>
-        <v>0.89045840037086521</v>
+        <v>0.8904652177469935</v>
       </c>
       <c r="R27" s="7">
         <v>151002</v>
@@ -4839,14 +4839,14 @@
       </c>
       <c r="T27" s="17">
         <f t="shared" si="6"/>
-        <v>96124</v>
+        <v>96125</v>
       </c>
       <c r="U27" s="16">
-        <v>133165</v>
+        <v>133166</v>
       </c>
       <c r="V27" s="18">
         <f t="shared" si="7"/>
-        <v>0.88187573674520869</v>
+        <v>0.88188235917405067</v>
       </c>
       <c r="W27" s="7">
         <v>153079</v>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="Y27" s="17">
         <f t="shared" si="8"/>
-        <v>73997</v>
+        <v>73998</v>
       </c>
       <c r="Z27" s="16">
-        <v>135050</v>
+        <v>135051</v>
       </c>
       <c r="AA27" s="18">
         <f t="shared" si="9"/>
-        <v>0.88222421102829263</v>
+        <v>0.88223074360297626</v>
       </c>
       <c r="AB27" s="28">
         <v>156081</v>
@@ -4873,14 +4873,14 @@
       </c>
       <c r="AD27" s="17">
         <f t="shared" si="10"/>
-        <v>52686</v>
+        <v>52687</v>
       </c>
       <c r="AE27" s="40">
-        <v>135661</v>
+        <v>135662</v>
       </c>
       <c r="AF27" s="18">
         <f t="shared" si="11"/>
-        <v>0.86917049480718345</v>
+        <v>0.86917690173691864</v>
       </c>
       <c r="AG27" s="16">
         <v>159400</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="AI27" s="17">
         <f t="shared" si="12"/>
-        <v>49922</v>
+        <v>49923</v>
       </c>
       <c r="AJ27" s="16">
-        <v>137433</v>
+        <v>137434</v>
       </c>
       <c r="AK27" s="18">
         <f t="shared" si="13"/>
-        <v>0.86218946047678791</v>
+        <v>0.86219573400250937</v>
       </c>
       <c r="AL27" s="30">
         <v>161009</v>
@@ -4907,14 +4907,14 @@
       </c>
       <c r="AN27" s="17">
         <f t="shared" si="14"/>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="AO27" s="16">
-        <v>138970</v>
+        <v>138971</v>
       </c>
       <c r="AP27" s="18">
         <f t="shared" si="15"/>
-        <v>0.86311945294983505</v>
+        <v>0.86312566378276989</v>
       </c>
       <c r="AQ27" s="32">
         <v>161396</v>
@@ -4924,14 +4924,14 @@
       </c>
       <c r="AS27" s="17">
         <f t="shared" si="16"/>
-        <v>42505</v>
+        <v>42506</v>
       </c>
       <c r="AT27" s="16">
-        <v>140879</v>
+        <v>140880</v>
       </c>
       <c r="AU27" s="18">
         <f t="shared" si="17"/>
-        <v>0.87287789040620589</v>
+        <v>0.87288408634662573</v>
       </c>
       <c r="AV27" s="34">
         <v>108346</v>
@@ -4941,14 +4941,14 @@
       </c>
       <c r="AX27" s="17">
         <f t="shared" si="18"/>
-        <v>41832</v>
+        <v>41833</v>
       </c>
       <c r="AY27" s="19">
-        <v>89133</v>
+        <v>89134</v>
       </c>
       <c r="AZ27" s="18">
         <f t="shared" si="19"/>
-        <v>0.82266996474258391</v>
+        <v>0.82267919443265092</v>
       </c>
       <c r="BA27" s="36">
         <v>101792</v>
@@ -4958,14 +4958,14 @@
       </c>
       <c r="BC27" s="17">
         <f t="shared" si="20"/>
-        <v>36654</v>
+        <v>36655</v>
       </c>
       <c r="BD27" s="38">
-        <v>91028</v>
+        <v>91029</v>
       </c>
       <c r="BE27" s="18">
         <f t="shared" si="21"/>
-        <v>0.89425495127318455</v>
+        <v>0.8942647752279157</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4975,14 +4975,14 @@
       </c>
       <c r="BH27" s="17">
         <f t="shared" si="22"/>
-        <v>64498</v>
+        <v>64499</v>
       </c>
       <c r="BI27" s="19">
-        <v>145223</v>
+        <v>145224</v>
       </c>
       <c r="BJ27" s="18">
         <f t="shared" si="23"/>
-        <v>0.93540782346007434</v>
+        <v>0.93541426464241773</v>
       </c>
       <c r="BK27" s="2"/>
       <c r="BL27" s="2"/>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="AX30" s="17">
         <f t="shared" si="18"/>
-        <v>48129</v>
+        <v>48130</v>
       </c>
       <c r="AY30" s="19">
-        <v>121219</v>
+        <v>121220</v>
       </c>
       <c r="AZ30" s="18">
         <f t="shared" si="19"/>
-        <v>0.88699858043933211</v>
+        <v>0.88700589776236261</v>
       </c>
       <c r="BA30" s="36">
         <v>130439</v>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="BC30" s="17">
         <f t="shared" si="20"/>
-        <v>39073</v>
+        <v>39074</v>
       </c>
       <c r="BD30" s="38">
-        <v>124156</v>
+        <v>124157</v>
       </c>
       <c r="BE30" s="18">
         <f t="shared" si="21"/>
-        <v>0.9518318907688651</v>
+        <v>0.9518395571876509</v>
       </c>
       <c r="BF30" s="9">
         <v>245647</v>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="BH30" s="17">
         <f t="shared" si="22"/>
-        <v>73633</v>
+        <v>73634</v>
       </c>
       <c r="BI30" s="19">
-        <v>239376</v>
+        <v>239377</v>
       </c>
       <c r="BJ30" s="18">
         <f t="shared" si="23"/>
-        <v>0.97447149771827057</v>
+        <v>0.97447556860047135</v>
       </c>
       <c r="BK30" s="2"/>
       <c r="BL30" s="2"/>
@@ -5729,14 +5729,14 @@
       </c>
       <c r="AD31" s="17">
         <f t="shared" si="10"/>
-        <v>42491</v>
+        <v>42493</v>
       </c>
       <c r="AE31" s="40">
-        <v>106238</v>
+        <v>106240</v>
       </c>
       <c r="AF31" s="18">
         <f t="shared" si="11"/>
-        <v>0.9360258680693222</v>
+        <v>0.93604348936995041</v>
       </c>
       <c r="AG31" s="16">
         <v>114692</v>
@@ -5926,14 +5926,14 @@
       </c>
       <c r="Y32" s="17">
         <f t="shared" si="8"/>
-        <v>157705</v>
+        <v>157706</v>
       </c>
       <c r="Z32" s="16">
-        <v>353409</v>
+        <v>353410</v>
       </c>
       <c r="AA32" s="18">
         <f t="shared" si="9"/>
-        <v>0.96614742804654008</v>
+        <v>0.96615016184060887</v>
       </c>
       <c r="AB32" s="28">
         <v>374326</v>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="AD32" s="17">
         <f t="shared" si="10"/>
-        <v>102608</v>
+        <v>102609</v>
       </c>
       <c r="AE32" s="40">
-        <v>357464</v>
+        <v>357465</v>
       </c>
       <c r="AF32" s="18">
         <f t="shared" si="11"/>
-        <v>0.95495370345634556</v>
+        <v>0.954956374924531</v>
       </c>
       <c r="AG32" s="16">
         <v>378033</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="AI32" s="17">
         <f t="shared" si="12"/>
-        <v>106965</v>
+        <v>106967</v>
       </c>
       <c r="AJ32" s="16">
-        <v>361248</v>
+        <v>361250</v>
       </c>
       <c r="AK32" s="18">
         <f t="shared" si="13"/>
-        <v>0.9555991143630318</v>
+        <v>0.95560440490644993</v>
       </c>
       <c r="AL32" s="30">
         <v>379234</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="AN32" s="17">
         <f t="shared" si="14"/>
-        <v>87002</v>
+        <v>87003</v>
       </c>
       <c r="AO32" s="16">
-        <v>364236</v>
+        <v>364237</v>
       </c>
       <c r="AP32" s="18">
         <f t="shared" si="15"/>
-        <v>0.96045185821946344</v>
+        <v>0.96045449511383474</v>
       </c>
       <c r="AQ32" s="32">
         <v>378853</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="AS32" s="17">
         <f t="shared" si="16"/>
-        <v>66678</v>
+        <v>66679</v>
       </c>
       <c r="AT32" s="16">
-        <v>367414</v>
+        <v>367415</v>
       </c>
       <c r="AU32" s="18">
         <f t="shared" si="17"/>
-        <v>0.96980623091278151</v>
+        <v>0.96980887045899067</v>
       </c>
       <c r="AV32" s="34">
         <v>171701</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="AX32" s="17">
         <f t="shared" si="18"/>
-        <v>56837</v>
+        <v>56838</v>
       </c>
       <c r="AY32" s="19">
-        <v>162896</v>
+        <v>162897</v>
       </c>
       <c r="AZ32" s="18">
         <f t="shared" si="19"/>
-        <v>0.94871899406526461</v>
+        <v>0.94872481814316745</v>
       </c>
       <c r="BA32" s="36">
         <v>169194</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="BC32" s="17">
         <f t="shared" si="20"/>
-        <v>50524</v>
+        <v>50525</v>
       </c>
       <c r="BD32" s="38">
-        <v>167335</v>
+        <v>167336</v>
       </c>
       <c r="BE32" s="18">
         <f t="shared" si="21"/>
-        <v>0.98901261274040453</v>
+        <v>0.98901852311547689</v>
       </c>
       <c r="BF32" s="9">
         <v>378386</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="BH32" s="17">
         <f t="shared" si="22"/>
-        <v>176862</v>
+        <v>176864</v>
       </c>
       <c r="BI32" s="19">
-        <v>376705</v>
+        <v>376707</v>
       </c>
       <c r="BJ32" s="18">
         <f t="shared" si="23"/>
-        <v>0.99555744662857504</v>
+        <v>0.99556273223639358</v>
       </c>
       <c r="BK32" s="2"/>
       <c r="BL32" s="2"/>
@@ -6072,14 +6072,14 @@
       </c>
       <c r="E33" s="17">
         <f t="shared" si="0"/>
-        <v>808071</v>
+        <v>808072</v>
       </c>
       <c r="F33" s="16">
-        <v>845892</v>
+        <v>845893</v>
       </c>
       <c r="G33" s="18">
         <f t="shared" si="1"/>
-        <v>0.94789072987940304</v>
+        <v>0.94789185046067093</v>
       </c>
       <c r="H33" s="7">
         <v>888497</v>
@@ -6106,14 +6106,14 @@
       </c>
       <c r="O33" s="17">
         <f t="shared" si="4"/>
-        <v>454208</v>
+        <v>454209</v>
       </c>
       <c r="P33" s="16">
-        <v>850271</v>
+        <v>850272</v>
       </c>
       <c r="Q33" s="18">
         <f t="shared" si="5"/>
-        <v>0.95673988457517978</v>
+        <v>0.95674100979276866</v>
       </c>
       <c r="R33" s="7">
         <v>899174</v>
@@ -6123,14 +6123,14 @@
       </c>
       <c r="T33" s="17">
         <f t="shared" si="6"/>
-        <v>425251</v>
+        <v>425252</v>
       </c>
       <c r="U33" s="16">
-        <v>858926</v>
+        <v>858927</v>
       </c>
       <c r="V33" s="18">
         <f t="shared" si="7"/>
-        <v>0.95523891927480109</v>
+        <v>0.95524003140660207</v>
       </c>
       <c r="W33" s="7">
         <v>909355</v>
@@ -6140,14 +6140,14 @@
       </c>
       <c r="Y33" s="17">
         <f t="shared" si="8"/>
-        <v>280860</v>
+        <v>280861</v>
       </c>
       <c r="Z33" s="16">
-        <v>867300</v>
+        <v>867301</v>
       </c>
       <c r="AA33" s="18">
         <f t="shared" si="9"/>
-        <v>0.9537529347724486</v>
+        <v>0.95375403445299145</v>
       </c>
       <c r="AB33" s="28">
         <v>919225</v>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="E36" s="17">
         <f t="shared" si="0"/>
-        <v>1190292</v>
+        <v>1190294</v>
       </c>
       <c r="F36" s="16">
-        <v>1261907</v>
+        <v>1261909</v>
       </c>
       <c r="G36" s="18">
         <f t="shared" si="1"/>
-        <v>0.91463612629576962</v>
+        <v>0.91463757590517236</v>
       </c>
       <c r="H36" s="7">
         <v>1370063</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="J36" s="17">
         <f t="shared" si="2"/>
-        <v>1054975</v>
+        <v>1054977</v>
       </c>
       <c r="K36" s="16">
-        <v>1261870</v>
+        <v>1261872</v>
       </c>
       <c r="L36" s="18">
         <f t="shared" si="3"/>
-        <v>0.92103063873705082</v>
+        <v>0.92103209852393653</v>
       </c>
       <c r="M36" s="7">
         <v>1376699</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="O36" s="17">
         <f t="shared" si="4"/>
-        <v>909598</v>
+        <v>909600</v>
       </c>
       <c r="P36" s="16">
-        <v>1267355</v>
+        <v>1267357</v>
       </c>
       <c r="Q36" s="18">
         <f t="shared" si="5"/>
-        <v>0.92057523104178907</v>
+        <v>0.92057668379217239</v>
       </c>
       <c r="R36" s="7">
         <v>1386159</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="T36" s="17">
         <f t="shared" si="6"/>
-        <v>856808</v>
+        <v>856810</v>
       </c>
       <c r="U36" s="16">
-        <v>1274725</v>
+        <v>1274727</v>
       </c>
       <c r="V36" s="18">
         <f t="shared" si="7"/>
-        <v>0.91960951088583631</v>
+        <v>0.91961095372175916</v>
       </c>
       <c r="W36" s="7">
         <v>1395892</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="Y36" s="17">
         <f t="shared" si="8"/>
-        <v>663049</v>
+        <v>663050</v>
       </c>
       <c r="Z36" s="16">
-        <v>1283932</v>
+        <v>1283933</v>
       </c>
       <c r="AA36" s="18">
         <f t="shared" si="9"/>
-        <v>0.91979322182518419</v>
+        <v>0.91979393821298494</v>
       </c>
       <c r="AB36" s="28">
         <v>1408098</v>
@@ -6783,14 +6783,14 @@
       </c>
       <c r="AD36" s="17">
         <f t="shared" si="10"/>
-        <v>434762</v>
+        <v>434765</v>
       </c>
       <c r="AE36" s="40">
-        <v>1290862</v>
+        <v>1290865</v>
       </c>
       <c r="AF36" s="18">
         <f t="shared" si="11"/>
-        <v>0.91674159042907521</v>
+        <v>0.91674372096260348</v>
       </c>
       <c r="AG36" s="16">
         <v>1413160</v>
@@ -6800,14 +6800,14 @@
       </c>
       <c r="AI36" s="17">
         <f t="shared" si="12"/>
-        <v>420944</v>
+        <v>420945</v>
       </c>
       <c r="AJ36" s="16">
-        <v>1299773</v>
+        <v>1299774</v>
       </c>
       <c r="AK36" s="18">
         <f t="shared" si="13"/>
-        <v>0.91976350873220303</v>
+        <v>0.91976421636615813</v>
       </c>
       <c r="AL36" s="30">
         <v>1410829</v>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="AN36" s="17">
         <f t="shared" si="14"/>
-        <v>358687</v>
+        <v>358688</v>
       </c>
       <c r="AO36" s="16">
-        <v>1310055</v>
+        <v>1310056</v>
       </c>
       <c r="AP36" s="18">
         <f t="shared" si="15"/>
-        <v>0.92857107416986751</v>
+        <v>0.92857178297298959</v>
       </c>
       <c r="AQ36" s="32">
         <v>1406326</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="AS36" s="17">
         <f t="shared" si="16"/>
-        <v>299744</v>
+        <v>299745</v>
       </c>
       <c r="AT36" s="16">
-        <v>1321867</v>
+        <v>1321868</v>
       </c>
       <c r="AU36" s="18">
         <f t="shared" si="17"/>
-        <v>0.93994351238617502</v>
+        <v>0.93994422345885664</v>
       </c>
       <c r="AV36" s="34">
         <v>685252</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="AX36" s="17">
         <f t="shared" si="18"/>
-        <v>251684</v>
+        <v>251685</v>
       </c>
       <c r="AY36" s="19">
-        <v>635326</v>
+        <v>635327</v>
       </c>
       <c r="AZ36" s="18">
         <f t="shared" si="19"/>
-        <v>0.92714213165375658</v>
+        <v>0.92714359097091292</v>
       </c>
       <c r="BA36" s="36">
         <v>667048</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="BC36" s="17">
         <f t="shared" si="20"/>
-        <v>222486</v>
+        <v>222489</v>
       </c>
       <c r="BD36" s="38">
-        <v>648505</v>
+        <v>648508</v>
       </c>
       <c r="BE36" s="18">
         <f t="shared" si="21"/>
-        <v>0.97220140079874307</v>
+        <v>0.97220589822621462</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="BH36" s="17">
         <f t="shared" si="22"/>
-        <v>477192</v>
+        <v>477195</v>
       </c>
       <c r="BI36" s="19">
-        <v>1343317</v>
+        <v>1343320</v>
       </c>
       <c r="BJ36" s="18">
         <f t="shared" si="23"/>
-        <v>0.98484156443618109</v>
+        <v>0.98484376386095818</v>
       </c>
       <c r="BK36" s="2"/>
       <c r="BL36" s="2"/>
@@ -6912,14 +6912,14 @@
       </c>
       <c r="E37" s="17">
         <f t="shared" si="0"/>
-        <v>576555</v>
+        <v>576557</v>
       </c>
       <c r="F37" s="16">
-        <v>676215</v>
+        <v>676217</v>
       </c>
       <c r="G37" s="18">
         <f t="shared" si="1"/>
-        <v>0.92147470838329881</v>
+        <v>0.9214774337730296</v>
       </c>
       <c r="H37" s="7">
         <v>729493</v>
@@ -6929,14 +6929,14 @@
       </c>
       <c r="J37" s="17">
         <f t="shared" si="2"/>
-        <v>474089</v>
+        <v>474091</v>
       </c>
       <c r="K37" s="16">
-        <v>677782</v>
+        <v>677784</v>
       </c>
       <c r="L37" s="18">
         <f t="shared" si="3"/>
-        <v>0.92911378176349879</v>
+        <v>0.92911652339364459</v>
       </c>
       <c r="M37" s="7">
         <v>737436</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="O37" s="17">
         <f t="shared" si="4"/>
-        <v>446526</v>
+        <v>446528</v>
       </c>
       <c r="P37" s="16">
-        <v>683926</v>
+        <v>683928</v>
       </c>
       <c r="Q37" s="18">
         <f t="shared" si="5"/>
-        <v>0.92743777087096368</v>
+        <v>0.92744048297072557</v>
       </c>
       <c r="R37" s="7">
         <v>746987</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="T37" s="17">
         <f t="shared" si="6"/>
-        <v>392171</v>
+        <v>392174</v>
       </c>
       <c r="U37" s="16">
-        <v>689287</v>
+        <v>689290</v>
       </c>
       <c r="V37" s="18">
         <f t="shared" si="7"/>
-        <v>0.92275635318954685</v>
+        <v>0.92276036932369643</v>
       </c>
       <c r="W37" s="7">
         <v>758127</v>
@@ -6980,14 +6980,14 @@
       </c>
       <c r="Y37" s="17">
         <f t="shared" si="8"/>
-        <v>268434</v>
+        <v>268436</v>
       </c>
       <c r="Z37" s="16">
-        <v>695640</v>
+        <v>695642</v>
       </c>
       <c r="AA37" s="18">
         <f t="shared" si="9"/>
-        <v>0.91757713417408959</v>
+        <v>0.9175797722545167</v>
       </c>
       <c r="AB37" s="28">
         <v>768520</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="AD37" s="17">
         <f t="shared" si="10"/>
-        <v>196243</v>
+        <v>196245</v>
       </c>
       <c r="AE37" s="40">
-        <v>701725</v>
+        <v>701727</v>
       </c>
       <c r="AF37" s="18">
         <f t="shared" si="11"/>
-        <v>0.91308619164107641</v>
+        <v>0.9130887940456982</v>
       </c>
       <c r="AG37" s="16">
         <v>770579</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="AI37" s="17">
         <f t="shared" si="12"/>
-        <v>189649</v>
+        <v>189651</v>
       </c>
       <c r="AJ37" s="16">
-        <v>707550</v>
+        <v>707552</v>
       </c>
       <c r="AK37" s="18">
         <f t="shared" si="13"/>
-        <v>0.91820566093807388</v>
+        <v>0.91820825638902692</v>
       </c>
       <c r="AL37" s="30">
         <v>769439</v>
@@ -7031,14 +7031,14 @@
       </c>
       <c r="AN37" s="17">
         <f t="shared" si="14"/>
-        <v>166240</v>
+        <v>166241</v>
       </c>
       <c r="AO37" s="16">
-        <v>715097</v>
+        <v>715098</v>
       </c>
       <c r="AP37" s="18">
         <f t="shared" si="15"/>
-        <v>0.92937451831789131</v>
+        <v>0.9293758179660766</v>
       </c>
       <c r="AQ37" s="32">
         <v>769503</v>
@@ -7048,14 +7048,14 @@
       </c>
       <c r="AS37" s="17">
         <f t="shared" si="16"/>
-        <v>134996</v>
+        <v>134999</v>
       </c>
       <c r="AT37" s="16">
-        <v>720389</v>
+        <v>720392</v>
       </c>
       <c r="AU37" s="18">
         <f t="shared" si="17"/>
-        <v>0.93617438788412777</v>
+        <v>0.93617828650440604</v>
       </c>
       <c r="AV37" s="34">
         <v>526548</v>
@@ -7065,14 +7065,14 @@
       </c>
       <c r="AX37" s="17">
         <f t="shared" si="18"/>
-        <v>135682</v>
+        <v>135683</v>
       </c>
       <c r="AY37" s="19">
-        <v>487949</v>
+        <v>487950</v>
       </c>
       <c r="AZ37" s="18">
         <f t="shared" si="19"/>
-        <v>0.92669424250020893</v>
+        <v>0.92669614166229863</v>
       </c>
       <c r="BA37" s="36">
         <v>525083</v>
@@ -7082,14 +7082,14 @@
       </c>
       <c r="BC37" s="17">
         <f t="shared" si="20"/>
-        <v>117162</v>
+        <v>117163</v>
       </c>
       <c r="BD37" s="38">
-        <v>495942</v>
+        <v>495943</v>
       </c>
       <c r="BE37" s="18">
         <f t="shared" si="21"/>
-        <v>0.94450210728589579</v>
+        <v>0.94450401174671428</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7099,14 +7099,14 @@
       </c>
       <c r="BH37" s="17">
         <f t="shared" si="22"/>
-        <v>198990</v>
+        <v>198991</v>
       </c>
       <c r="BI37" s="19">
-        <v>738863</v>
+        <v>738864</v>
       </c>
       <c r="BJ37" s="18">
         <f t="shared" si="23"/>
-        <v>0.96543393129905652</v>
+        <v>0.96543523794715136</v>
       </c>
       <c r="BK37" s="2"/>
       <c r="BL37" s="2"/>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="AN40" s="17">
         <f t="shared" si="14"/>
-        <v>85459</v>
+        <v>85460</v>
       </c>
       <c r="AO40" s="16">
-        <v>294972</v>
+        <v>294973</v>
       </c>
       <c r="AP40" s="18">
         <f t="shared" si="15"/>
-        <v>0.92296716741084694</v>
+        <v>0.9229702964100992</v>
       </c>
       <c r="AQ40" s="32">
         <v>320883</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="AS40" s="17">
         <f t="shared" si="16"/>
-        <v>70111</v>
+        <v>70113</v>
       </c>
       <c r="AT40" s="16">
-        <v>298158</v>
+        <v>298160</v>
       </c>
       <c r="AU40" s="18">
         <f t="shared" si="17"/>
-        <v>0.92917979450453903</v>
+        <v>0.92918602730590283</v>
       </c>
       <c r="AV40" s="34">
         <v>237285</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="AX40" s="17">
         <f t="shared" si="18"/>
-        <v>72826</v>
+        <v>72827</v>
       </c>
       <c r="AY40" s="19">
-        <v>218388</v>
+        <v>218389</v>
       </c>
       <c r="AZ40" s="18">
         <f t="shared" si="19"/>
-        <v>0.92036159049244581</v>
+        <v>0.92036580483384955</v>
       </c>
       <c r="BA40" s="36">
         <v>231667</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="BC40" s="17">
         <f t="shared" si="20"/>
-        <v>66788</v>
+        <v>66789</v>
       </c>
       <c r="BD40" s="38">
-        <v>220886</v>
+        <v>220887</v>
       </c>
       <c r="BE40" s="18">
         <f t="shared" si="21"/>
-        <v>0.95346337631168876</v>
+        <v>0.95346769285224053</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="BH40" s="17">
         <f t="shared" si="22"/>
-        <v>110216</v>
+        <v>110218</v>
       </c>
       <c r="BI40" s="19">
-        <v>305165</v>
+        <v>305167</v>
       </c>
       <c r="BJ40" s="18">
         <f t="shared" si="23"/>
-        <v>0.97065437623850559</v>
+        <v>0.97066073774376493</v>
       </c>
       <c r="BK40" s="2"/>
       <c r="BL40" s="2"/>
@@ -7768,14 +7768,14 @@
       </c>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
-        <v>721682</v>
+        <v>721701</v>
       </c>
       <c r="F41" s="16">
-        <v>811864</v>
+        <v>811883</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="1"/>
-        <v>0.92695892838385263</v>
+        <v>0.92698062194292086</v>
       </c>
       <c r="H41" s="7">
         <v>872102</v>
@@ -7785,14 +7785,14 @@
       </c>
       <c r="J41" s="17">
         <f t="shared" si="2"/>
-        <v>601156</v>
+        <v>601176</v>
       </c>
       <c r="K41" s="16">
-        <v>812807</v>
+        <v>812827</v>
       </c>
       <c r="L41" s="18">
         <f t="shared" si="3"/>
-        <v>0.93200909985299885</v>
+        <v>0.93203203295027415</v>
       </c>
       <c r="M41" s="7">
         <v>879453</v>
@@ -7802,14 +7802,14 @@
       </c>
       <c r="O41" s="17">
         <f t="shared" si="4"/>
-        <v>529817</v>
+        <v>529837</v>
       </c>
       <c r="P41" s="16">
-        <v>817903</v>
+        <v>817923</v>
       </c>
       <c r="Q41" s="18">
         <f t="shared" si="5"/>
-        <v>0.93001331509472362</v>
+        <v>0.93003605650330379</v>
       </c>
       <c r="R41" s="7">
         <v>900135</v>
@@ -7819,14 +7819,14 @@
       </c>
       <c r="T41" s="17">
         <f t="shared" si="6"/>
-        <v>493899</v>
+        <v>493918</v>
       </c>
       <c r="U41" s="16">
-        <v>829364</v>
+        <v>829383</v>
       </c>
       <c r="V41" s="18">
         <f t="shared" si="7"/>
-        <v>0.92137734895321255</v>
+        <v>0.92139845689813193</v>
       </c>
       <c r="W41" s="7">
         <v>916182</v>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="Y41" s="17">
         <f t="shared" si="8"/>
-        <v>333137</v>
+        <v>333159</v>
       </c>
       <c r="Z41" s="16">
-        <v>837183</v>
+        <v>837205</v>
       </c>
       <c r="AA41" s="18">
         <f t="shared" si="9"/>
-        <v>0.91377368252159508</v>
+        <v>0.91379769521776244</v>
       </c>
       <c r="AB41" s="28">
         <v>928683</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="AD41" s="17">
         <f t="shared" si="10"/>
-        <v>228087</v>
+        <v>228106</v>
       </c>
       <c r="AE41" s="40">
-        <v>842874</v>
+        <v>842893</v>
       </c>
       <c r="AF41" s="18">
         <f t="shared" si="11"/>
-        <v>0.90760140973830683</v>
+        <v>0.90762186881853124</v>
       </c>
       <c r="AG41" s="16">
         <v>933135</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="AI41" s="17">
         <f t="shared" si="12"/>
-        <v>223169</v>
+        <v>223190</v>
       </c>
       <c r="AJ41" s="16">
-        <v>851117</v>
+        <v>851138</v>
       </c>
       <c r="AK41" s="18">
         <f t="shared" si="13"/>
-        <v>0.91210489371848658</v>
+        <v>0.91212739850075286</v>
       </c>
       <c r="AL41" s="30">
         <v>933314</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="AN41" s="17">
         <f t="shared" si="14"/>
-        <v>186885</v>
+        <v>186904</v>
       </c>
       <c r="AO41" s="16">
-        <v>858768</v>
+        <v>858787</v>
       </c>
       <c r="AP41" s="18">
         <f t="shared" si="15"/>
-        <v>0.92012763121521801</v>
+        <v>0.92014798877976756</v>
       </c>
       <c r="AQ41" s="32">
         <v>923873</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="AS41" s="17">
         <f t="shared" si="16"/>
-        <v>168501</v>
+        <v>168517</v>
       </c>
       <c r="AT41" s="16">
-        <v>867896</v>
+        <v>867912</v>
       </c>
       <c r="AU41" s="18">
         <f t="shared" si="17"/>
-        <v>0.93941050339169996</v>
+        <v>0.93942782178935846</v>
       </c>
       <c r="AV41" s="34">
         <v>726285</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AX41" s="17">
         <f t="shared" si="18"/>
-        <v>161063</v>
+        <v>161074</v>
       </c>
       <c r="AY41" s="19">
-        <v>680700</v>
+        <v>680711</v>
       </c>
       <c r="AZ41" s="18">
         <f t="shared" si="19"/>
-        <v>0.9372353828042711</v>
+        <v>0.9372505283738477</v>
       </c>
       <c r="BA41" s="36">
         <v>715063</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="BC41" s="17">
         <f t="shared" si="20"/>
-        <v>142471</v>
+        <v>142481</v>
       </c>
       <c r="BD41" s="38">
-        <v>688378</v>
+        <v>688388</v>
       </c>
       <c r="BE41" s="18">
         <f t="shared" si="21"/>
-        <v>0.96268160987213713</v>
+        <v>0.96269559465389765</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="BH41" s="17">
         <f t="shared" si="22"/>
-        <v>228695</v>
+        <v>228705</v>
       </c>
       <c r="BI41" s="19">
-        <v>888004</v>
+        <v>888014</v>
       </c>
       <c r="BJ41" s="18">
         <f t="shared" si="23"/>
-        <v>0.97489117606696862</v>
+        <v>0.97490215452175111</v>
       </c>
       <c r="BK41" s="2"/>
       <c r="BL41" s="2"/>
@@ -8196,14 +8196,14 @@
       </c>
       <c r="E43" s="17">
         <f t="shared" si="0"/>
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="F43" s="16">
-        <v>3525</v>
+        <v>3527</v>
       </c>
       <c r="G43" s="18">
         <f t="shared" si="1"/>
-        <v>0.91534666320436253</v>
+        <v>0.91586600882887559</v>
       </c>
       <c r="H43" s="7">
         <v>3844</v>
@@ -8213,14 +8213,14 @@
       </c>
       <c r="J43" s="17">
         <f t="shared" si="2"/>
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="K43" s="16">
-        <v>3516</v>
+        <v>3518</v>
       </c>
       <c r="L43" s="18">
         <f t="shared" si="3"/>
-        <v>0.91467221644120711</v>
+        <v>0.91519250780437045</v>
       </c>
       <c r="M43" s="7">
         <v>3825</v>
@@ -8230,14 +8230,14 @@
       </c>
       <c r="O43" s="17">
         <f t="shared" si="4"/>
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="P43" s="16">
-        <v>3542</v>
+        <v>3544</v>
       </c>
       <c r="Q43" s="18">
         <f t="shared" si="5"/>
-        <v>0.92601307189542481</v>
+        <v>0.92653594771241832</v>
       </c>
       <c r="R43" s="7">
         <v>3845</v>
@@ -8247,14 +8247,14 @@
       </c>
       <c r="T43" s="17">
         <f t="shared" si="6"/>
-        <v>2978</v>
+        <v>2980</v>
       </c>
       <c r="U43" s="16">
-        <v>3554</v>
+        <v>3556</v>
       </c>
       <c r="V43" s="18">
         <f t="shared" si="7"/>
-        <v>0.92431729518855654</v>
+        <v>0.92483745123537064</v>
       </c>
       <c r="W43" s="7">
         <v>3856</v>
@@ -8264,14 +8264,14 @@
       </c>
       <c r="Y43" s="17">
         <f t="shared" si="8"/>
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="Z43" s="16">
-        <v>3552</v>
+        <v>3554</v>
       </c>
       <c r="AA43" s="18">
         <f t="shared" si="9"/>
-        <v>0.92116182572614103</v>
+        <v>0.92168049792531115</v>
       </c>
       <c r="AB43" s="28">
         <v>3868</v>
@@ -8281,14 +8281,14 @@
       </c>
       <c r="AD43" s="17">
         <f t="shared" si="10"/>
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="AE43" s="40">
-        <v>3557</v>
+        <v>3559</v>
       </c>
       <c r="AF43" s="18">
         <f t="shared" si="11"/>
-        <v>0.91959669079627715</v>
+        <v>0.92011375387797312</v>
       </c>
       <c r="AG43" s="16">
         <v>3955</v>
@@ -8298,14 +8298,14 @@
       </c>
       <c r="AI43" s="17">
         <f t="shared" si="12"/>
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="AJ43" s="16">
-        <v>3592</v>
+        <v>3594</v>
       </c>
       <c r="AK43" s="18">
         <f t="shared" si="13"/>
-        <v>0.90821744627054357</v>
+        <v>0.90872313527180781</v>
       </c>
       <c r="AL43" s="30">
         <v>3994</v>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="AN43" s="17">
         <f t="shared" si="14"/>
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="AO43" s="16">
-        <v>3616</v>
+        <v>3618</v>
       </c>
       <c r="AP43" s="18">
         <f t="shared" si="15"/>
-        <v>0.90535803705558338</v>
+        <v>0.90585878818227339</v>
       </c>
       <c r="AQ43" s="32">
         <v>4014</v>
@@ -8332,14 +8332,14 @@
       </c>
       <c r="AS43" s="17">
         <f t="shared" si="16"/>
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="AT43" s="16">
-        <v>3644</v>
+        <v>3646</v>
       </c>
       <c r="AU43" s="18">
         <f t="shared" si="17"/>
-        <v>0.90782262082710519</v>
+        <v>0.90832087693074237</v>
       </c>
       <c r="AV43" s="34">
         <v>3140</v>
@@ -8349,14 +8349,14 @@
       </c>
       <c r="AX43" s="17">
         <f t="shared" si="18"/>
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="AY43" s="19">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="AZ43" s="18">
         <f t="shared" si="19"/>
-        <v>0.88980891719745225</v>
+        <v>0.89012738853503182</v>
       </c>
       <c r="BA43" s="36">
         <v>3099</v>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="BC43" s="17">
         <f t="shared" si="20"/>
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="BD43" s="38">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="BE43" s="18">
         <f t="shared" si="21"/>
-        <v>0.91319780574378828</v>
+        <v>0.91352049048080031</v>
       </c>
       <c r="BF43" s="9">
         <v>3984</v>
@@ -8383,14 +8383,14 @@
       </c>
       <c r="BH43" s="17">
         <f t="shared" si="22"/>
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="BI43" s="19">
-        <v>3712</v>
+        <v>3713</v>
       </c>
       <c r="BJ43" s="18">
         <f t="shared" si="23"/>
-        <v>0.93172690763052213</v>
+        <v>0.93197791164658639</v>
       </c>
       <c r="BK43" s="2"/>
       <c r="BL43" s="2"/>
@@ -8410,14 +8410,14 @@
       </c>
       <c r="E44" s="17">
         <f t="shared" si="0"/>
-        <v>260727</v>
+        <v>260728</v>
       </c>
       <c r="F44" s="16">
-        <v>302639</v>
+        <v>302640</v>
       </c>
       <c r="G44" s="18">
         <f t="shared" si="1"/>
-        <v>0.84690036910695143</v>
+        <v>0.84690316749172379</v>
       </c>
       <c r="H44" s="7">
         <v>355488</v>
@@ -8427,14 +8427,14 @@
       </c>
       <c r="J44" s="17">
         <f t="shared" si="2"/>
-        <v>218367</v>
+        <v>218368</v>
       </c>
       <c r="K44" s="16">
-        <v>302999</v>
+        <v>303000</v>
       </c>
       <c r="L44" s="18">
         <f t="shared" si="3"/>
-        <v>0.85234663336033845</v>
+        <v>0.85234944639481502</v>
       </c>
       <c r="M44" s="7">
         <v>358237</v>
@@ -8444,14 +8444,14 @@
       </c>
       <c r="O44" s="17">
         <f t="shared" si="4"/>
-        <v>188417</v>
+        <v>188418</v>
       </c>
       <c r="P44" s="16">
-        <v>305086</v>
+        <v>305087</v>
       </c>
       <c r="Q44" s="18">
         <f t="shared" si="5"/>
-        <v>0.85163174099827765</v>
+        <v>0.8516345324463972</v>
       </c>
       <c r="R44" s="7">
         <v>364550</v>
@@ -8461,14 +8461,14 @@
       </c>
       <c r="T44" s="17">
         <f t="shared" si="6"/>
-        <v>191973</v>
+        <v>191974</v>
       </c>
       <c r="U44" s="16">
-        <v>309031</v>
+        <v>309032</v>
       </c>
       <c r="V44" s="18">
         <f t="shared" si="7"/>
-        <v>0.84770539020710467</v>
+        <v>0.84770813331504591</v>
       </c>
       <c r="W44" s="7">
         <v>368236</v>
@@ -8478,14 +8478,14 @@
       </c>
       <c r="Y44" s="17">
         <f t="shared" si="8"/>
-        <v>140616</v>
+        <v>140617</v>
       </c>
       <c r="Z44" s="16">
-        <v>311933</v>
+        <v>311934</v>
       </c>
       <c r="AA44" s="18">
         <f t="shared" si="9"/>
-        <v>0.84710077233078784</v>
+        <v>0.84710348798053425</v>
       </c>
       <c r="AB44" s="28">
         <v>371659</v>
@@ -8495,14 +8495,14 @@
       </c>
       <c r="AD44" s="17">
         <f t="shared" si="10"/>
-        <v>118502</v>
+        <v>118503</v>
       </c>
       <c r="AE44" s="40">
-        <v>314151</v>
+        <v>314152</v>
       </c>
       <c r="AF44" s="18">
         <f t="shared" si="11"/>
-        <v>0.8452667633502754</v>
+        <v>0.84526945398873699</v>
       </c>
       <c r="AG44" s="16">
         <v>376783</v>
@@ -8512,14 +8512,14 @@
       </c>
       <c r="AI44" s="17">
         <f t="shared" si="12"/>
-        <v>113634</v>
+        <v>113635</v>
       </c>
       <c r="AJ44" s="16">
-        <v>317578</v>
+        <v>317579</v>
       </c>
       <c r="AK44" s="18">
         <f t="shared" si="13"/>
-        <v>0.84286711449295748</v>
+        <v>0.84286976854051265</v>
       </c>
       <c r="AL44" s="30">
         <v>379786</v>
@@ -8529,14 +8529,14 @@
       </c>
       <c r="AN44" s="17">
         <f t="shared" si="14"/>
-        <v>102488</v>
+        <v>102489</v>
       </c>
       <c r="AO44" s="16">
-        <v>321780</v>
+        <v>321781</v>
       </c>
       <c r="AP44" s="18">
         <f t="shared" si="15"/>
-        <v>0.84726661856940488</v>
+        <v>0.84726925163118172</v>
       </c>
       <c r="AQ44" s="32">
         <v>381213</v>
@@ -8546,14 +8546,14 @@
       </c>
       <c r="AS44" s="17">
         <f t="shared" si="16"/>
-        <v>84199</v>
+        <v>84200</v>
       </c>
       <c r="AT44" s="16">
-        <v>325858</v>
+        <v>325859</v>
       </c>
       <c r="AU44" s="18">
         <f t="shared" si="17"/>
-        <v>0.85479246510481022</v>
+        <v>0.85479508831020978</v>
       </c>
       <c r="AV44" s="34">
         <v>286191</v>
@@ -8563,14 +8563,14 @@
       </c>
       <c r="AX44" s="17">
         <f t="shared" si="18"/>
-        <v>80539</v>
+        <v>80540</v>
       </c>
       <c r="AY44" s="19">
-        <v>240010</v>
+        <v>240011</v>
       </c>
       <c r="AZ44" s="18">
         <f t="shared" si="19"/>
-        <v>0.83863573627402677</v>
+        <v>0.83863923044400412</v>
       </c>
       <c r="BA44" s="36">
         <v>282649</v>
@@ -8597,14 +8597,14 @@
       </c>
       <c r="BH44" s="17">
         <f t="shared" si="22"/>
-        <v>115090</v>
+        <v>115091</v>
       </c>
       <c r="BI44" s="19">
-        <v>334888</v>
+        <v>334889</v>
       </c>
       <c r="BJ44" s="18">
         <f t="shared" si="23"/>
-        <v>0.89983743769564573</v>
+        <v>0.89984012467588304</v>
       </c>
       <c r="BK44" s="2"/>
       <c r="BL44" s="2"/>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="T45" s="17">
         <f t="shared" si="6"/>
-        <v>161921</v>
+        <v>161922</v>
       </c>
       <c r="U45" s="16">
-        <v>256513</v>
+        <v>256514</v>
       </c>
       <c r="V45" s="18">
         <f t="shared" si="7"/>
-        <v>0.89722800328792041</v>
+        <v>0.8972315010755697</v>
       </c>
       <c r="W45" s="7">
         <v>289101</v>
@@ -8692,14 +8692,14 @@
       </c>
       <c r="Y45" s="17">
         <f t="shared" si="8"/>
-        <v>106878</v>
+        <v>106879</v>
       </c>
       <c r="Z45" s="16">
-        <v>258051</v>
+        <v>258052</v>
       </c>
       <c r="AA45" s="18">
         <f t="shared" si="9"/>
-        <v>0.89259808855728617</v>
+        <v>0.89260154755604437</v>
       </c>
       <c r="AB45" s="28">
         <v>291802</v>
@@ -8709,14 +8709,14 @@
       </c>
       <c r="AD45" s="17">
         <f t="shared" si="10"/>
-        <v>82915</v>
+        <v>82916</v>
       </c>
       <c r="AE45" s="40">
-        <v>259336</v>
+        <v>259337</v>
       </c>
       <c r="AF45" s="18">
         <f t="shared" si="11"/>
-        <v>0.8887396248140863</v>
+        <v>0.88874305179539548</v>
       </c>
       <c r="AG45" s="16">
         <v>295238</v>
@@ -8811,14 +8811,14 @@
       </c>
       <c r="BH45" s="17">
         <f t="shared" si="22"/>
-        <v>88683</v>
+        <v>88684</v>
       </c>
       <c r="BI45" s="19">
-        <v>272423</v>
+        <v>272424</v>
       </c>
       <c r="BJ45" s="18">
         <f t="shared" si="23"/>
-        <v>0.9371147283835104</v>
+        <v>0.93711816830865757</v>
       </c>
       <c r="BK45" s="2"/>
       <c r="BL45" s="2"/>
@@ -9266,15 +9266,15 @@
       </c>
       <c r="E48" s="24">
         <f>F48-D48</f>
-        <v>8669740</v>
+        <v>8669770</v>
       </c>
       <c r="F48" s="25">
         <f>SUM(F10:F47)</f>
-        <v>9532909</v>
+        <v>9532939</v>
       </c>
       <c r="G48" s="26">
         <f>F48/C48</f>
-        <v>0.9153704875707479</v>
+        <v>0.91537336823546711</v>
       </c>
       <c r="H48" s="27">
         <f>SUM(H10:H47)</f>
@@ -9286,15 +9286,15 @@
       </c>
       <c r="J48" s="24">
         <f t="shared" si="2"/>
-        <v>7138819</v>
+        <v>7138850</v>
       </c>
       <c r="K48" s="25">
         <f>SUM(K10:K47)</f>
-        <v>9536331</v>
+        <v>9536362</v>
       </c>
       <c r="L48" s="26">
         <f t="shared" si="3"/>
-        <v>0.92202515563952159</v>
+        <v>0.92202815289075213</v>
       </c>
       <c r="M48" s="27">
         <f>SUM(M10:M47)</f>
@@ -9306,15 +9306,15 @@
       </c>
       <c r="O48" s="24">
         <f t="shared" si="4"/>
-        <v>6148872</v>
+        <v>6148905</v>
       </c>
       <c r="P48" s="25">
         <f>SUM(P10:P47)</f>
-        <v>9600153</v>
+        <v>9600186</v>
       </c>
       <c r="Q48" s="26">
         <f t="shared" si="5"/>
-        <v>0.92326039596276199</v>
+        <v>0.92326356961979306</v>
       </c>
       <c r="R48" s="27">
         <f>SUM(R10:R47)</f>
@@ -9326,15 +9326,15 @@
       </c>
       <c r="T48" s="24">
         <f t="shared" si="6"/>
-        <v>5911146</v>
+        <v>5911179</v>
       </c>
       <c r="U48" s="25">
         <f>SUM(U10:U47)</f>
-        <v>9713694</v>
+        <v>9713727</v>
       </c>
       <c r="V48" s="26">
         <f t="shared" si="7"/>
-        <v>0.91933547195507859</v>
+        <v>0.91933859518199657</v>
       </c>
       <c r="W48" s="27">
         <f>SUM(W10:W47)</f>
@@ -9346,15 +9346,15 @@
       </c>
       <c r="Y48" s="24">
         <f t="shared" si="8"/>
-        <v>4169284</v>
+        <v>4169319</v>
       </c>
       <c r="Z48" s="25">
         <f>SUM(Z10:Z47)</f>
-        <v>9814885</v>
+        <v>9814920</v>
       </c>
       <c r="AA48" s="26">
         <f t="shared" si="9"/>
-        <v>0.91689696012633237</v>
+        <v>0.91690022979211094</v>
       </c>
       <c r="AB48" s="27">
         <f>SUM(AB10:AB47)</f>
@@ -9366,15 +9366,15 @@
       </c>
       <c r="AD48" s="24">
         <f t="shared" si="10"/>
-        <v>2784220</v>
+        <v>2784256</v>
       </c>
       <c r="AE48" s="25">
         <f>SUM(AE10:AE47)</f>
-        <v>9902016</v>
+        <v>9902052</v>
       </c>
       <c r="AF48" s="26">
         <f t="shared" si="11"/>
-        <v>0.91254359273232366</v>
+        <v>0.91254691039706359</v>
       </c>
       <c r="AG48" s="23">
         <f>SUM(AG10:AG47)</f>
@@ -9386,15 +9386,15 @@
       </c>
       <c r="AI48" s="24">
         <f t="shared" si="12"/>
-        <v>2740731</v>
+        <v>2740766</v>
       </c>
       <c r="AJ48" s="25">
         <f>SUM(AJ10:AJ47)</f>
-        <v>10005701</v>
+        <v>10005736</v>
       </c>
       <c r="AK48" s="26">
         <f t="shared" si="13"/>
-        <v>0.91194940981274497</v>
+        <v>0.91195259981705779</v>
       </c>
       <c r="AL48" s="27">
         <f>SUM(AL10:AL47)</f>
@@ -9406,15 +9406,15 @@
       </c>
       <c r="AN48" s="24">
         <f t="shared" si="14"/>
-        <v>2318201</v>
+        <v>2318235</v>
       </c>
       <c r="AO48" s="25">
         <f>SUM(AO10:AO47)</f>
-        <v>10099962</v>
+        <v>10099996</v>
       </c>
       <c r="AP48" s="26">
         <f t="shared" si="15"/>
-        <v>0.91729709130355486</v>
+        <v>0.91730017924597529</v>
       </c>
       <c r="AQ48" s="27">
         <f>SUM(AQ10:AQ47)</f>
@@ -9426,15 +9426,15 @@
       </c>
       <c r="AS48" s="24">
         <f t="shared" si="16"/>
-        <v>1958768</v>
+        <v>1958802</v>
       </c>
       <c r="AT48" s="25">
         <f>SUM(AT10:AT47)</f>
-        <v>10194213</v>
+        <v>10194247</v>
       </c>
       <c r="AU48" s="26">
         <f t="shared" si="17"/>
-        <v>0.92807851340114089</v>
+        <v>0.92808160875234225</v>
       </c>
       <c r="AV48" s="27">
         <f>SUM(AV10:AV47)</f>
@@ -9446,15 +9446,15 @@
       </c>
       <c r="AX48" s="24">
         <f t="shared" si="18"/>
-        <v>1826867</v>
+        <v>1826890</v>
       </c>
       <c r="AY48" s="25">
         <f>SUM(AY10:AY47)</f>
-        <v>5622766</v>
+        <v>5622789</v>
       </c>
       <c r="AZ48" s="26">
         <f t="shared" si="19"/>
-        <v>0.8980959668973254</v>
+        <v>0.89809964057096558</v>
       </c>
       <c r="BA48" s="27">
         <f>SUM(BA10:BA47)</f>
@@ -9466,15 +9466,15 @@
       </c>
       <c r="BC48" s="24">
         <f t="shared" si="20"/>
-        <v>1571207</v>
+        <v>1571234</v>
       </c>
       <c r="BD48" s="25">
         <f>SUM(BD10:BD47)</f>
-        <v>5732079</v>
+        <v>5732106</v>
       </c>
       <c r="BE48" s="26">
         <f t="shared" si="21"/>
-        <v>0.93469335974093759</v>
+        <v>0.9346977624577727</v>
       </c>
       <c r="BF48" s="27">
         <f>SUM(BF10:BF47)</f>
@@ -9486,15 +9486,15 @@
       </c>
       <c r="BH48" s="24">
         <f t="shared" si="22"/>
-        <v>3236240</v>
+        <v>3236271</v>
       </c>
       <c r="BI48" s="25">
         <f>SUM(BI10:BI47)</f>
-        <v>10408164</v>
+        <v>10408195</v>
       </c>
       <c r="BJ48" s="26">
         <f t="shared" si="23"/>
-        <v>0.96554421446543892</v>
+        <v>0.96554709027241592</v>
       </c>
       <c r="BK48" s="10"/>
       <c r="BL48" s="10"/>
